--- a/data/precios_magnesio_bisglicinato.xlsx
+++ b/data/precios_magnesio_bisglicinato.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46245.69794615355</v>
+        <v>46245.69794615741</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -471,6 +471,66 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>8,00 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46246.40221327546</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bisglicinato de magnesio</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>100mg de magnesio</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8,47 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46247.40486964121</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bisglicinato de magnesio</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>100mg de magnesio</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8,47 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46248.39678553241</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bisglicinato de magnesio</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>100mg de magnesio</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8,47 €</t>
         </is>
       </c>
     </row>
